--- a/crates/xlstream-eval/tests/fixtures/operators/arithmetic.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/operators/arithmetic.xlsx
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">val</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amt</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
   </si>
   <si>
     <t xml:space="preserve">add</t>
@@ -43,7 +40,10 @@
     <t xml:space="preserve">div</t>
   </si>
   <si>
-    <t xml:space="preserve">exp</t>
+    <t xml:space="preserve">div_zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">power</t>
   </si>
   <si>
     <t xml:space="preserve">pct</t>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">pos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">double_neg</t>
   </si>
 </sst>
 </file>
@@ -330,7 +333,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -367,40 +370,44 @@
       <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>1000</v>
+        <f aca="false">A2+B2</f>
+        <v>13</v>
       </c>
       <c r="D2" s="0" t="n">
-        <f aca="false">A2+B2</f>
-        <v>13.5</v>
+        <f aca="false">A2-B2</f>
+        <v>7</v>
       </c>
       <c r="E2" s="0" t="n">
-        <f aca="false">A2-B2</f>
-        <v>6.5</v>
+        <f aca="false">A2*B2</f>
+        <v>30</v>
       </c>
       <c r="F2" s="0" t="n">
-        <f aca="false">A2*B2</f>
-        <v>35</v>
-      </c>
-      <c r="G2" s="0" t="n">
         <f aca="false">A2/B2</f>
-        <v>2.85714285714286</v>
+        <v>3.33333333333333</v>
+      </c>
+      <c r="G2" s="0" t="e">
+        <f aca="false">A2/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H2" s="0" t="n">
         <f aca="false">A2^2</f>
         <v>100</v>
       </c>
       <c r="I2" s="1" t="n">
-        <f aca="false">C2%</f>
-        <v>10</v>
+        <f aca="false">B2%</f>
+        <v>0.03</v>
       </c>
       <c r="J2" s="0" t="n">
         <f aca="false">-A2</f>
@@ -410,91 +417,105 @@
         <f aca="false">+A2</f>
         <v>10</v>
       </c>
+      <c r="L2" s="0" t="n">
+        <f aca="false">--A2</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>2500</v>
+        <f aca="false">A3+B3</f>
+        <v>5</v>
       </c>
       <c r="D3" s="0" t="n">
-        <f aca="false">A3+B3</f>
-        <v>32.2</v>
+        <f aca="false">A3-B3</f>
+        <v>-5</v>
       </c>
       <c r="E3" s="0" t="n">
-        <f aca="false">A3-B3</f>
-        <v>17.8</v>
+        <f aca="false">A3*B3</f>
+        <v>0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <f aca="false">A3*B3</f>
-        <v>180</v>
-      </c>
-      <c r="G3" s="0" t="n">
         <f aca="false">A3/B3</f>
-        <v>3.47222222222222</v>
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="e">
+        <f aca="false">A3/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H3" s="0" t="n">
         <f aca="false">A3^2</f>
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <f aca="false">C3%</f>
-        <v>25</v>
+        <f aca="false">B3%</f>
+        <v>0.05</v>
       </c>
       <c r="J3" s="0" t="n">
         <f aca="false">-A3</f>
-        <v>-25</v>
+        <v>-0</v>
       </c>
       <c r="K3" s="0" t="n">
         <f aca="false">+A3</f>
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <f aca="false">--A3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0</v>
+        <f aca="false">A4+B4</f>
+        <v>-5</v>
       </c>
       <c r="D4" s="0" t="n">
-        <f aca="false">A4+B4</f>
-        <v>0</v>
+        <f aca="false">A4-B4</f>
+        <v>-9</v>
       </c>
       <c r="E4" s="0" t="n">
-        <f aca="false">A4-B4</f>
-        <v>0</v>
+        <f aca="false">A4*B4</f>
+        <v>-14</v>
       </c>
       <c r="F4" s="0" t="n">
-        <f aca="false">A4*B4</f>
-        <v>0</v>
+        <f aca="false">A4/B4</f>
+        <v>-3.5</v>
       </c>
       <c r="G4" s="0" t="e">
-        <f aca="false">A4/B4</f>
+        <f aca="false">A4/0</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H4" s="0" t="n">
         <f aca="false">A4^2</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1" t="n">
-        <f aca="false">C4%</f>
-        <v>0</v>
+        <f aca="false">B4%</f>
+        <v>0.02</v>
       </c>
       <c r="J4" s="0" t="n">
         <f aca="false">-A4</f>
-        <v>-0</v>
+        <v>7</v>
       </c>
       <c r="K4" s="0" t="n">
         <f aca="false">+A4</f>
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <f aca="false">--A4</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -502,34 +523,35 @@
         <v>100</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>15.8</v>
+        <v>-4</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>5000</v>
+        <f aca="false">A5+B5</f>
+        <v>96</v>
       </c>
       <c r="D5" s="0" t="n">
-        <f aca="false">A5+B5</f>
-        <v>115.8</v>
+        <f aca="false">A5-B5</f>
+        <v>104</v>
       </c>
       <c r="E5" s="0" t="n">
-        <f aca="false">A5-B5</f>
-        <v>84.2</v>
+        <f aca="false">A5*B5</f>
+        <v>-400</v>
       </c>
       <c r="F5" s="0" t="n">
-        <f aca="false">A5*B5</f>
-        <v>1580</v>
-      </c>
-      <c r="G5" s="0" t="n">
         <f aca="false">A5/B5</f>
-        <v>6.32911392405063</v>
+        <v>-25</v>
+      </c>
+      <c r="G5" s="0" t="e">
+        <f aca="false">A5/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H5" s="0" t="n">
         <f aca="false">A5^2</f>
         <v>10000</v>
       </c>
       <c r="I5" s="1" t="n">
-        <f aca="false">C5%</f>
-        <v>50</v>
+        <f aca="false">B5%</f>
+        <v>-0.04</v>
       </c>
       <c r="J5" s="0" t="n">
         <f aca="false">-A5</f>
@@ -539,134 +561,153 @@
         <f aca="false">+A5</f>
         <v>100</v>
       </c>
+      <c r="L5" s="0" t="n">
+        <f aca="false">--A5</f>
+        <v>100</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
+        <v>3.5</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>-2.3</v>
+        <v>1.5</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>150</v>
+        <f aca="false">A6+B6</f>
+        <v>5</v>
       </c>
       <c r="D6" s="0" t="n">
-        <f aca="false">A6+B6</f>
-        <v>-7.3</v>
+        <f aca="false">A6-B6</f>
+        <v>2</v>
       </c>
       <c r="E6" s="0" t="n">
-        <f aca="false">A6-B6</f>
-        <v>-2.7</v>
+        <f aca="false">A6*B6</f>
+        <v>5.25</v>
       </c>
       <c r="F6" s="0" t="n">
-        <f aca="false">A6*B6</f>
-        <v>11.5</v>
-      </c>
-      <c r="G6" s="0" t="n">
         <f aca="false">A6/B6</f>
-        <v>2.17391304347826</v>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="G6" s="0" t="e">
+        <f aca="false">A6/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">A6^2</f>
-        <v>25</v>
+        <v>12.25</v>
       </c>
       <c r="I6" s="1" t="n">
-        <f aca="false">C6%</f>
-        <v>1.5</v>
+        <f aca="false">B6%</f>
+        <v>0.015</v>
       </c>
       <c r="J6" s="0" t="n">
         <f aca="false">-A6</f>
-        <v>5</v>
+        <v>-3.5</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">+A6</f>
-        <v>-5</v>
+        <v>3.5</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <f aca="false">--A6</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>999</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>3000</v>
+        <f aca="false">A7+B7</f>
+        <v>999.1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <f aca="false">A7+B7</f>
-        <v>58.1</v>
+        <f aca="false">A7-B7</f>
+        <v>998.9</v>
       </c>
       <c r="E7" s="0" t="n">
-        <f aca="false">A7-B7</f>
-        <v>41.9</v>
+        <f aca="false">A7*B7</f>
+        <v>99.9</v>
       </c>
       <c r="F7" s="0" t="n">
-        <f aca="false">A7*B7</f>
-        <v>405</v>
-      </c>
-      <c r="G7" s="0" t="n">
         <f aca="false">A7/B7</f>
-        <v>6.17283950617284</v>
+        <v>9990</v>
+      </c>
+      <c r="G7" s="0" t="e">
+        <f aca="false">A7/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H7" s="0" t="n">
         <f aca="false">A7^2</f>
-        <v>2500</v>
+        <v>998001</v>
       </c>
       <c r="I7" s="1" t="n">
-        <f aca="false">C7%</f>
-        <v>30</v>
+        <f aca="false">B7%</f>
+        <v>0.001</v>
       </c>
       <c r="J7" s="0" t="n">
         <f aca="false">-A7</f>
-        <v>-50</v>
+        <v>-999</v>
       </c>
       <c r="K7" s="0" t="n">
         <f aca="false">+A7</f>
-        <v>50</v>
+        <v>999</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <f aca="false">--A7</f>
+        <v>999</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>4.6</v>
+        <v>-8</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>7500</v>
+        <f aca="false">A8+B8</f>
+        <v>-58</v>
       </c>
       <c r="D8" s="0" t="n">
-        <f aca="false">A8+B8</f>
-        <v>79.6</v>
+        <f aca="false">A8-B8</f>
+        <v>-42</v>
       </c>
       <c r="E8" s="0" t="n">
-        <f aca="false">A8-B8</f>
-        <v>70.4</v>
+        <f aca="false">A8*B8</f>
+        <v>400</v>
       </c>
       <c r="F8" s="0" t="n">
-        <f aca="false">A8*B8</f>
-        <v>345</v>
-      </c>
-      <c r="G8" s="0" t="n">
         <f aca="false">A8/B8</f>
-        <v>16.304347826087</v>
+        <v>6.25</v>
+      </c>
+      <c r="G8" s="0" t="e">
+        <f aca="false">A8/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">A8^2</f>
-        <v>5625</v>
+        <v>2500</v>
       </c>
       <c r="I8" s="1" t="n">
-        <f aca="false">C8%</f>
-        <v>75</v>
+        <f aca="false">B8%</f>
+        <v>-0.08</v>
       </c>
       <c r="J8" s="0" t="n">
         <f aca="false">-A8</f>
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">+A8</f>
-        <v>75</v>
+        <v>-50</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <f aca="false">--A8</f>
+        <v>-50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -674,34 +715,35 @@
         <v>1</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>250</v>
+        <f aca="false">A9+B9</f>
+        <v>2</v>
       </c>
       <c r="D9" s="0" t="n">
-        <f aca="false">A9+B9</f>
-        <v>1.5</v>
+        <f aca="false">A9-B9</f>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <f aca="false">A9-B9</f>
-        <v>0.5</v>
+        <f aca="false">A9*B9</f>
+        <v>1</v>
       </c>
       <c r="F9" s="0" t="n">
-        <f aca="false">A9*B9</f>
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="0" t="n">
         <f aca="false">A9/B9</f>
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="e">
+        <f aca="false">A9/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H9" s="0" t="n">
         <f aca="false">A9^2</f>
         <v>1</v>
       </c>
       <c r="I9" s="1" t="n">
-        <f aca="false">C9%</f>
-        <v>2.5</v>
+        <f aca="false">B9%</f>
+        <v>0.01</v>
       </c>
       <c r="J9" s="0" t="n">
         <f aca="false">-A9</f>
@@ -711,48 +753,57 @@
         <f aca="false">+A9</f>
         <v>1</v>
       </c>
+      <c r="L9" s="0" t="n">
+        <f aca="false">--A9</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>4000</v>
+        <f aca="false">A10+B10</f>
+        <v>0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <f aca="false">A10+B10</f>
-        <v>1011.4</v>
+        <f aca="false">A10-B10</f>
+        <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <f aca="false">A10-B10</f>
-        <v>986.6</v>
-      </c>
-      <c r="F10" s="0" t="n">
         <f aca="false">A10*B10</f>
-        <v>12387.6</v>
-      </c>
-      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="e">
         <f aca="false">A10/B10</f>
-        <v>80.5645161290323</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="0" t="e">
+        <f aca="false">A10/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H10" s="0" t="n">
         <f aca="false">A10^2</f>
-        <v>998001</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1" t="n">
-        <f aca="false">C10%</f>
-        <v>40</v>
+        <f aca="false">B10%</f>
+        <v>0</v>
       </c>
       <c r="J10" s="0" t="n">
         <f aca="false">-A10</f>
-        <v>-999</v>
+        <v>-0</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">+A10</f>
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <f aca="false">--A10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -760,34 +811,35 @@
         <v>42</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>1200</v>
+        <f aca="false">A11+B11</f>
+        <v>49</v>
       </c>
       <c r="D11" s="0" t="n">
-        <f aca="false">A11+B11</f>
-        <v>48.7</v>
+        <f aca="false">A11-B11</f>
+        <v>35</v>
       </c>
       <c r="E11" s="0" t="n">
-        <f aca="false">A11-B11</f>
-        <v>35.3</v>
+        <f aca="false">A11*B11</f>
+        <v>294</v>
       </c>
       <c r="F11" s="0" t="n">
-        <f aca="false">A11*B11</f>
-        <v>281.4</v>
-      </c>
-      <c r="G11" s="0" t="n">
         <f aca="false">A11/B11</f>
-        <v>6.26865671641791</v>
+        <v>6</v>
+      </c>
+      <c r="G11" s="0" t="e">
+        <f aca="false">A11/0</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="H11" s="0" t="n">
         <f aca="false">A11^2</f>
         <v>1764</v>
       </c>
       <c r="I11" s="1" t="n">
-        <f aca="false">C11%</f>
-        <v>12</v>
+        <f aca="false">B11%</f>
+        <v>0.07</v>
       </c>
       <c r="J11" s="0" t="n">
         <f aca="false">-A11</f>
@@ -795,6 +847,10 @@
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">+A11</f>
+        <v>42</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">--A11</f>
         <v>42</v>
       </c>
     </row>
